--- a/assets/template_upload_harga_manual.xlsx
+++ b/assets/template_upload_harga_manual.xlsx
@@ -437,15 +437,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="30" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -456,25 +457,30 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>Barcode</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>PCCode</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>NamaProduk</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>JenisHarga</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>NamaKompetitor</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Harga</t>
         </is>
@@ -488,21 +494,26 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
+          <t>8999999026400</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
           <t>64840063</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>DOVE DEEPLY NOURISH PUMP RL 6X2X550ML</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>Unilever</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr"/>
-      <c r="F2" s="2" t="n">
+      <c r="F2" s="2" t="inlineStr"/>
+      <c r="G2" s="2" t="n">
         <v>42000</v>
       </c>
     </row>
@@ -514,25 +525,30 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
+          <t>8999999026400</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
           <t>64840063</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>DOVE DEEPLY NOURISH PUMP RL 6X2X550ML</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>Kompetitor</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>Wardah - Hair Shampoo 550ml</t>
         </is>
       </c>
-      <c r="F3" s="2" t="n">
+      <c r="G3" s="2" t="n">
         <v>39000</v>
       </c>
     </row>
@@ -544,82 +560,101 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
+          <t>8999999035273</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
           <t>69965241</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>VASELINE HB SPF30 PPF VIT SRM 8X3X180ML</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>Unilever</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr"/>
-      <c r="F4" s="2" t="n">
+      <c r="F4" s="2" t="inlineStr"/>
+      <c r="G4" s="2" t="n">
         <v>25000</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>Catatan: kolom WAJIB -- PCCode dan Harga. Kolom lain membantu tapi tidak wajib.</t>
+          <t>Catatan: kolom WAJIB -- Barcode (atau PCCode kalau Barcode tidak ada) dan Harga.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>JenisHarga isi 'Unilever' atau 'Kompetitor' (kalau dikosongkan dianggap Unilever).</t>
+          <t>Barcode LEBIH DIUTAMAKAN daripada PCCode -- 1 PCCode kadang menaungi beberapa</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>Untuk baris Kompetitor: NamaKompetitor harus SAMA PERSIS dengan yang sudah terdaftar</t>
+          <t xml:space="preserve">  barcode/varian sekaligus, jadi Barcode lebih akurat untuk mencocokkan harga produk.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  di app (format 'Brand - Nama Produk'), atau cukup nama Brand-nya saja kalau unik.</t>
+          <t>JenisHarga isi 'Unilever' atau 'Kompetitor' (kalau dikosongkan dianggap Unilever).</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Kalau kompetitornya belum pernah ditambahkan di app, tambahkan dulu lewat tombol</t>
+          <t>Untuk baris Kompetitor: NamaKompetitor harus SAMA PERSIS dengan yang sudah terdaftar</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  '+ Tambah kompetitor' di produk itu, baru bisa diisi harganya lewat file ini.</t>
+          <t xml:space="preserve">  di app (format 'Brand - Nama Produk'), atau cukup nama Brand-nya saja kalau unik.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>Kolom Toko opsional -- kalau diisi, baris yang tokonya beda dari yang sedang dipilih di</t>
+          <t xml:space="preserve">  Kalau kompetitornya belum pernah ditambahkan di app, tambahkan dulu lewat tombol</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  app akan diabaikan otomatis (jadi file hasil Export semua toko bisa diupload lagi apa adanya).</t>
+          <t xml:space="preserve">  '+ Tambah kompetitor' di produk itu, baru bisa diisi harganya lewat file ini.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>Kolom Toko opsional -- kalau diisi, baris yang tokonya beda dari yang sedang dipilih di</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  app akan diabaikan otomatis (jadi file hasil Export semua toko bisa diupload lagi apa adanya).</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
         <is>
           <t>File ini berlaku untuk toko &amp; bulan yang SEDANG DIPILIH di halaman Survei Harga saat upload.</t>
         </is>
